--- a/diseases/d112/2015-2019.xlsx
+++ b/diseases/d112/2015-2019.xlsx
@@ -12309,9 +12309,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -13593,9 +13590,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -14877,9 +14871,6 @@
       <c r="O96" t="n">
         <v>6</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.06046387887875783</v>
       </c>
@@ -16309,9 +16300,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -17593,9 +17581,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -18877,9 +18862,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -20309,9 +20291,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -21593,9 +21572,6 @@
       <c r="O138" t="n">
         <v>3</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -22877,9 +22853,6 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01007731314645964</v>
       </c>
@@ -24309,9 +24282,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -25593,9 +25563,6 @@
       <c r="O163" t="n">
         <v>3</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -26877,9 +26844,6 @@
       <c r="O171" t="n">
         <v>3</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.03023193943937891</v>
       </c>
@@ -28536,9 +28500,6 @@
       <c r="O181" t="n">
         <v>14</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.1391945991700124</v>
       </c>
@@ -30047,9 +30008,6 @@
       <c r="O190" t="n">
         <v>9</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.08948224232357942</v>
       </c>
@@ -31558,9 +31516,6 @@
       <c r="O199" t="n">
         <v>6</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.05965482821571962</v>
       </c>
@@ -33217,9 +33172,6 @@
       <c r="O209" t="n">
         <v>4</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.03976988547714641</v>
       </c>
@@ -34728,9 +34680,6 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -36239,9 +36188,6 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -37898,9 +37844,6 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -39409,9 +39352,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -41068,9 +41008,6 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.009942471369286603</v>
       </c>
@@ -42579,9 +42516,6 @@
       <c r="O265" t="n">
         <v>2</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -44090,9 +44024,6 @@
       <c r="O274" t="n">
         <v>2</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -45749,9 +45680,6 @@
       <c r="O284" t="n">
         <v>2</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.01988494273857321</v>
       </c>
@@ -47260,9 +47188,6 @@
       <c r="O293" t="n">
         <v>1</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0.009827619137892749</v>
       </c>
@@ -48771,9 +48696,6 @@
       <c r="O302" t="n">
         <v>2</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.0196552382757855</v>
       </c>
@@ -50282,9 +50204,6 @@
       <c r="O311" t="n">
         <v>6</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.0589657148273565</v>
       </c>
@@ -51941,9 +51860,6 @@
       <c r="O321" t="n">
         <v>1</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.009827619137892749</v>
       </c>
@@ -53452,9 +53368,6 @@
       <c r="O330" t="n">
         <v>3</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.02948285741367825</v>
       </c>
@@ -55111,9 +55024,6 @@
       <c r="O340" t="n">
         <v>2</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.0196552382757855</v>
       </c>
@@ -56622,9 +56532,6 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0</v>
       </c>
@@ -58133,9 +58040,6 @@
       <c r="O358" t="n">
         <v>1</v>
       </c>
-      <c r="Q358" t="n">
-        <v>0</v>
-      </c>
       <c r="R358" t="n">
         <v>0.009827619137892749</v>
       </c>
@@ -59792,9 +59696,6 @@
       <c r="O368" t="n">
         <v>0</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0</v>
       </c>
@@ -61303,9 +61204,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -62814,9 +62712,6 @@
       <c r="O386" t="n">
         <v>3</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0.02948285741367825</v>
       </c>
@@ -64473,9 +64368,6 @@
       <c r="O396" t="n">
         <v>18</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>0.1768971444820695</v>
       </c>
@@ -65984,9 +65876,6 @@
       <c r="O405" t="n">
         <v>19</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.1848406357545024</v>
       </c>
@@ -67643,9 +67532,6 @@
       <c r="O415" t="n">
         <v>14</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.1361983631875281</v>
       </c>
@@ -69302,9 +69188,6 @@
       <c r="O425" t="n">
         <v>11</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0.1070129996473435</v>
       </c>
@@ -70961,9 +70844,6 @@
       <c r="O435" t="n">
         <v>2</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0.01945690902678973</v>
       </c>
@@ -72472,9 +72352,6 @@
       <c r="O444" t="n">
         <v>2</v>
       </c>
-      <c r="Q444" t="n">
-        <v>0</v>
-      </c>
       <c r="R444" t="n">
         <v>0.01945690902678973</v>
       </c>
@@ -74131,9 +74008,6 @@
       <c r="O454" t="n">
         <v>8</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0.07782763610715893</v>
       </c>
@@ -75642,9 +75516,6 @@
       <c r="O463" t="n">
         <v>3</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>0.0291853635401846</v>
       </c>
@@ -77153,9 +77024,6 @@
       <c r="O472" t="n">
         <v>1</v>
       </c>
-      <c r="Q472" t="n">
-        <v>0</v>
-      </c>
       <c r="R472" t="n">
         <v>0.009728454513394866</v>
       </c>
@@ -78812,9 +78680,6 @@
       <c r="O482" t="n">
         <v>0</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0</v>
       </c>
@@ -80323,9 +80188,6 @@
       <c r="O491" t="n">
         <v>1</v>
       </c>
-      <c r="Q491" t="n">
-        <v>0</v>
-      </c>
       <c r="R491" t="n">
         <v>0.009728454513394866</v>
       </c>
@@ -81982,9 +81844,6 @@
       <c r="O501" t="n">
         <v>4</v>
       </c>
-      <c r="Q501" t="n">
-        <v>0</v>
-      </c>
       <c r="R501" t="n">
         <v>0.03891381805357946</v>
       </c>
@@ -83492,9 +83351,6 @@
       </c>
       <c r="O510" t="n">
         <v>12</v>
-      </c>
-      <c r="Q510" t="n">
-        <v>0</v>
       </c>
       <c r="R510" t="n">
         <v>0.1167414541607384</v>
